--- a/AAII_Financials/Yearly/PSTL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PSTL_YR_FIN.xlsx
@@ -2795,7 +2795,7 @@
         <v>15400</v>
       </c>
       <c r="E57" s="3">
-        <v>16100</v>
+        <v>14000</v>
       </c>
       <c r="F57" s="3">
         <v>10300</v>
@@ -2939,7 +2939,7 @@
         <v>20200</v>
       </c>
       <c r="E60" s="3">
-        <v>16500</v>
+        <v>14400</v>
       </c>
       <c r="F60" s="3">
         <v>11000</v>
@@ -2987,7 +2987,7 @@
         <v>362900</v>
       </c>
       <c r="E61" s="3">
-        <v>296600</v>
+        <v>298800</v>
       </c>
       <c r="F61" s="3">
         <v>241600</v>
